--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\豆包下载\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cv_mcp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15210" windowHeight="13275"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="招聘岗位信息" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="245">
   <si>
     <t>企业名称</t>
   </si>
@@ -677,6 +677,101 @@
   </si>
   <si>
     <t>中共党员；初会及以上职称；38周岁及以下</t>
+  </si>
+  <si>
+    <t>南开区私立高中</t>
+  </si>
+  <si>
+    <t>民企</t>
+  </si>
+  <si>
+    <t>班主任、教师、助教</t>
+  </si>
+  <si>
+    <t>天津南开区</t>
+  </si>
+  <si>
+    <t>班主任：女35-40（条件优秀者，放宽至45）有管理经验，心理咨询师者优先；教师岗要求高中教资、高中教学经验；助教岗：无教师资格证要求，工作期间表现优秀，并考取相应教资可转为正式老师
+助教和正式老师共同参加区教研活动，有正式老师带教</t>
+  </si>
+  <si>
+    <t>班主任：6.5k左右；教师岗：7-8k；助教岗：4k左右</t>
+  </si>
+  <si>
+    <t>2026.10.13</t>
+  </si>
+  <si>
+    <t>南开大学出版社</t>
+  </si>
+  <si>
+    <t>版权贸易干事（社聘合同制）</t>
+  </si>
+  <si>
+    <t>天津市南开区卫津路94号</t>
+  </si>
+  <si>
+    <t>本科及以上学历</t>
+  </si>
+  <si>
+    <t>外国语言文学、法学、经济学等相关专业优先</t>
+  </si>
+  <si>
+    <t>1.具备出色的英语听说读写能力，能熟练进行英文商务邮件往来、合同翻译及口头谈判，掌握第二外语者优先；
+2.熟悉国内外版权法律法规及国际出版贸易惯例，具备较强的商务谈判能力、跨文化沟通能力和合同风险把控意识，能熟练运用各种办公软件和网络工具；
+3.热爱出版事业，具备敏锐的市场洞察力、优秀的文字功底和团队协作精神，工作细致严谨，责任心强，能承受一定的工作压力；
+4.具有1-3年图书版权贸易、国际出版合作或相关外贸商务经验者优先；
+5.身体健康，能胜任本职工作。</t>
+  </si>
+  <si>
+    <t>五险一金、全勤奖、通讯补助、定期体检、高温补贴</t>
+  </si>
+  <si>
+    <t>动车安全员/乘警</t>
+  </si>
+  <si>
+    <t>高铁、动车安全员(乘警)</t>
+  </si>
+  <si>
+    <t>天津站、天津西站</t>
+  </si>
+  <si>
+    <t>中专、高中学历及以上</t>
+  </si>
+  <si>
+    <t>不限</t>
+  </si>
+  <si>
+    <t>1-3年相关从业经验</t>
+  </si>
+  <si>
+    <t>统一缴纳五险一金,福利体系完善，公司提供免费食宿，统一配发工装、被褥，宿舍配备空调、热水等齐全配套生活设施，住宿条件优良</t>
+  </si>
+  <si>
+    <t>天津机场防爆员</t>
+  </si>
+  <si>
+    <t>天津机场防爆员、文职</t>
+  </si>
+  <si>
+    <t>35周岁以下</t>
+  </si>
+  <si>
+    <t>五险一金足额缴纳，到手实发5000元，福利齐全 ，年终奖1-2万；食宿：单位全包吃住，零生活开销；作息：上1天，休1天，每天工时8小时</t>
+  </si>
+  <si>
+    <t>佳和康医院</t>
+  </si>
+  <si>
+    <t>护士岗</t>
+  </si>
+  <si>
+    <t>天津北辰区</t>
+  </si>
+  <si>
+    <t>35内，护士证，有经验优先</t>
+  </si>
+  <si>
+    <t>6-7K，五险一金</t>
   </si>
 </sst>
 </file>
@@ -689,7 +784,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,13 +803,6 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1188,152 +1276,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1343,6 +1431,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1690,19 +1781,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="49" customWidth="1"/>
-    <col min="6" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="1" max="1" width="37.125" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="3" max="3" width="47.75" customWidth="1"/>
+    <col min="4" max="4" width="33.125" customWidth="1"/>
+    <col min="5" max="5" width="47.75" customWidth="1"/>
+    <col min="6" max="6" width="49.375" customWidth="1"/>
+    <col min="7" max="7" width="49.5" customWidth="1"/>
+    <col min="8" max="8" width="129.375" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9">
+    <row r="1" ht="15" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2652,6 +2745,139 @@
         <v>16</v>
       </c>
     </row>
+    <row r="37" ht="67.5" spans="1:9">
+      <c r="A37" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H37" t="s">
+        <v>220</v>
+      </c>
+      <c r="I37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" ht="148.5" spans="1:9">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" t="s">
+        <v>226</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="H38" t="s">
+        <v>228</v>
+      </c>
+      <c r="I38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>230</v>
+      </c>
+      <c r="D39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" t="s">
+        <v>232</v>
+      </c>
+      <c r="F39" t="s">
+        <v>233</v>
+      </c>
+      <c r="G39" t="s">
+        <v>234</v>
+      </c>
+      <c r="H39" t="s">
+        <v>235</v>
+      </c>
+      <c r="I39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D41" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13395" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="招聘岗位信息" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="267">
   <si>
     <t>企业名称</t>
   </si>
@@ -772,6 +772,72 @@
   </si>
   <si>
     <t>6-7K，五险一金</t>
+  </si>
+  <si>
+    <t>方大医院</t>
+  </si>
+  <si>
+    <t>沈阳</t>
+  </si>
+  <si>
+    <t>30周岁以下，女士</t>
+  </si>
+  <si>
+    <t>4-5k，五险一金，排班制</t>
+  </si>
+  <si>
+    <t>2026.10.14</t>
+  </si>
+  <si>
+    <t>西青烟草局</t>
+  </si>
+  <si>
+    <t>某国企公司/党务/管理岗</t>
+  </si>
+  <si>
+    <t>党务/管理岗</t>
+  </si>
+  <si>
+    <t>天津南开区/水上公园附近</t>
+  </si>
+  <si>
+    <t>女性，40岁以下，文笔好</t>
+  </si>
+  <si>
+    <t>本科4500，研究生5000-5500，五险一金，正常班，管饭</t>
+  </si>
+  <si>
+    <t>2026.10.19</t>
+  </si>
+  <si>
+    <t>北京局天津段</t>
+  </si>
+  <si>
+    <t>客运段/机务段/供电段/电务段/车辆段/工务段/车务段</t>
+  </si>
+  <si>
+    <t>男172-184cm，女162-168cm;（根据学历/专业/匹配岗位）无犯罪记录/无纹身，28周岁及以下/ 男女不限</t>
+  </si>
+  <si>
+    <t>直签3/5/终身/五险一金/综合年薪：7-13（次年薪资上浮8-15%）</t>
+  </si>
+  <si>
+    <t>2026.10.20</t>
+  </si>
+  <si>
+    <t>天津烟草专卖局</t>
+  </si>
+  <si>
+    <t>专业技术岗/业务岗</t>
+  </si>
+  <si>
+    <t>天津和平区，红桥区，北辰区，滨海区，河东区，东丽区</t>
+  </si>
+  <si>
+    <t>（部分岗位）本科及以上学历/研究生及以上学历</t>
+  </si>
+  <si>
+    <t>性别不限，18-35周岁，（部分岗位）党员</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1847,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.125" customWidth="1"/>
@@ -1930,7 +1996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="33" spans="1:9">
+    <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -2090,7 +2156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" ht="33" spans="1:9">
+    <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>67</v>
       </c>
@@ -2146,7 +2212,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" ht="33" spans="1:9">
+    <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -2506,7 +2572,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" ht="33" spans="1:9">
+    <row r="28" ht="16.5" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>163</v>
       </c>
@@ -2641,7 +2707,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33" ht="33" spans="1:9">
+    <row r="33" ht="16.5" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>193</v>
       </c>
@@ -2695,7 +2761,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" ht="33" spans="1:9">
+    <row r="35" ht="16.5" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>207</v>
       </c>
@@ -2876,6 +2942,115 @@
       </c>
       <c r="I41" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" t="s">
+        <v>246</v>
+      </c>
+      <c r="E42" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H42" t="s">
+        <v>248</v>
+      </c>
+      <c r="I42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" t="s">
+        <v>254</v>
+      </c>
+      <c r="H44" t="s">
+        <v>255</v>
+      </c>
+      <c r="I44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>258</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>259</v>
+      </c>
+      <c r="H45" t="s">
+        <v>260</v>
+      </c>
+      <c r="I45" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" t="s">
+        <v>264</v>
+      </c>
+      <c r="E46" t="s">
+        <v>265</v>
+      </c>
+      <c r="G46" t="s">
+        <v>266</v>
+      </c>
+      <c r="I46" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
